--- a/data/processed_data/Video_613/contracciones_Video_613.xlsx
+++ b/data/processed_data/Video_613/contracciones_Video_613.xlsx
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,22 +425,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -795,327 +783,327 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>blur_px</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>blur_sigma</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1382,52 +1370,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1482,87 +1470,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1642,32 +1630,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1800,17 +1788,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>intervalo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
@@ -2084,27 +2072,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>junto_al_borde</t>
         </is>
@@ -2533,117 +2521,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -4416,112 +4404,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>

--- a/data/processed_data/Video_613/contracciones_Video_613.xlsx
+++ b/data/processed_data/Video_613/contracciones_Video_613.xlsx
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM2"/>
+  <dimension ref="A1:BN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,165 +945,170 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1260,53 +1265,53 @@
         </is>
       </c>
       <c r="AG2" t="n">
+        <v>0.3198999999999614</v>
+      </c>
+      <c r="AH2" t="n">
         <v>24</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.08083333333333131</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>24</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="b">
+        <v>0</v>
+      </c>
       <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0.06750000000000256</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
         </is>
       </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
@@ -1317,41 +1322,44 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="n">
         <v>2</v>
       </c>
-      <c r="BD2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="n">
+      <c r="BE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.09999999999999432</v>
       </c>
-      <c r="BF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1.5 s: sin meseta | 2 s: sin meseta | 3 s: sin meseta</t>
         </is>
       </c>
-      <c r="BH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr">
+      <c r="BI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>no hay meseta en el escaneo de k</t>
         </is>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>0.03617544000002103</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>0.04166105999999244</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>1.151639344261417</v>
       </c>
     </row>
@@ -4400,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4431,85 +4439,90 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
@@ -4536,46 +4549,49 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>0.3198999999999614</v>
+      </c>
+      <c r="G2" t="n">
         <v>24</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.08083333333333131</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0.06750000000000256</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
         </is>
@@ -4602,46 +4618,49 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>0.3198999999999614</v>
+      </c>
+      <c r="G3" t="n">
         <v>24</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.08083333333333131</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>24</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.06750000000000256</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
         </is>

--- a/data/processed_data/Video_613/contracciones_Video_613.xlsx
+++ b/data/processed_data/Video_613/contracciones_Video_613.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_613" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_613" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_613" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="trenes_Video_613" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="grilla_Video_613" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="espont_Video_613" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="eventos_Video_613" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cinetica_Video_613" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cin_grupos_Video_613" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_613" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_613" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_613" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trenes_Video_613" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_613" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="espont_Video_613" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_613" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="basal_Video_613" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_613" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cin_grupos_Video_613" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,13 +774,311 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1611924420344413</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.1371-0.1988</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.1395-0.182</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3198999999999614</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.08083333333333131</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.06750000000000256</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1611924420344413</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.1371-0.1988</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.1395-0.182</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3198999999999614</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.08083333333333131</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.06750000000000256</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN2"/>
+  <dimension ref="A1:BW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,172 +1244,217 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>amplitud_relativa_ic95_pct</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>ttp_ic95_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>rt50_ic95_s</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>eventos_junto_al_borde</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>motivo_no_reportable</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
         </is>
       </c>
     </row>
@@ -1264,103 +1608,132 @@
           <t>0.1371-0.1988</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.1395-0.182</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
         <v>0.3198999999999614</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>24</v>
       </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="b">
+        <v>0</v>
+      </c>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.08083333333333131</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AR2" t="n">
         <v>24</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.06750000000000256</v>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="n">
         <v>2</v>
       </c>
-      <c r="BE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="n">
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="n">
         <v>0.09999999999999432</v>
       </c>
-      <c r="BG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>1.5 s: sin meseta | 2 s: sin meseta | 3 s: sin meseta</t>
         </is>
       </c>
-      <c r="BI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>no hay meseta en el escaneo de k</t>
         </is>
       </c>
-      <c r="BL2" t="n">
+      <c r="BO2" t="n">
         <v>0.03617544000002103</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BP2" t="n">
         <v>0.04166105999999244</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BQ2" t="n">
         <v>1.151639344261417</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0-10 s</t>
+        </is>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.1957999999999629</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.09863145686649402</v>
+      </c>
+      <c r="BV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>no contable (conteo NO reportable); actividad basal 0.10 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,6 +2478,16 @@
           <t>junto_al_borde</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>en_promedio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>reportable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2121,6 +2504,12 @@
       </c>
       <c r="E2" t="b">
         <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2139,6 +2528,12 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2156,6 +2551,12 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2173,6 +2574,12 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2190,6 +2597,12 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2207,6 +2620,12 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2224,6 +2643,12 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2241,6 +2666,12 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2258,6 +2689,12 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2275,6 +2712,12 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2292,6 +2735,12 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2309,6 +2758,12 @@
       <c r="E13" t="b">
         <v>0</v>
       </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2326,6 +2781,12 @@
       <c r="E14" t="b">
         <v>0</v>
       </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2343,6 +2804,12 @@
       <c r="E15" t="b">
         <v>0</v>
       </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2360,6 +2827,12 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,6 +2850,12 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2873,12 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2411,6 +2896,12 @@
       <c r="E19" t="b">
         <v>0</v>
       </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2428,6 +2919,12 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2445,6 +2942,12 @@
       <c r="E21" t="b">
         <v>0</v>
       </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2462,6 +2965,12 @@
       <c r="E22" t="b">
         <v>0</v>
       </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2479,6 +2988,12 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2496,6 +3011,12 @@
       <c r="E24" t="b">
         <v>0</v>
       </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2511,6 +3032,12 @@
         <v>0</v>
       </c>
       <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2525,1876 +3052,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>evento</t>
+          <t>dato</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tren</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>basal_fin_s</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.3866666666666668</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.2597000000000094</v>
-      </c>
-      <c r="G2" t="n">
-        <v>198.4641410543336</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.1308548731374658</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3309397408858161</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.05572692578085076</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.09999999999999998</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.04061667954993881</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.09833333333333344</v>
-      </c>
-      <c r="T2" t="b">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4451275444473077</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.1141878035614916</v>
+          <t>10.0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>basal_definicion</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>42</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.386666666666667</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3187999999999533</v>
-      </c>
-      <c r="G3" t="n">
-        <v>198.5183571723238</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1605896827582646</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.357911405091201</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.02875526157546604</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.07833333333333403</v>
-      </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.01224688407034202</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.07833333333333403</v>
-      </c>
-      <c r="T3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.408711057993282</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.05079965290208155</v>
+          <t>0-10 s</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_px</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>62</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.053333333333334</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.2863000000000397</v>
-      </c>
-      <c r="G4" t="n">
-        <v>198.5208372907626</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.144216599077059</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.02053837342497</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.0327949599083639</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.06666666666666687</v>
-      </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.02055866724112887</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.06666666666666687</v>
-      </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.127349999999997</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.106811626575027</v>
+          <t>0.1957999999999629</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>basal_actividad_p95_pct</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>87</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.886666666666667</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.2531000000000176</v>
-      </c>
-      <c r="G5" t="n">
-        <v>198.5215471224989</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1274924579566372</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.874383316741331</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.01228334992533586</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.06166666666666698</v>
-      </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.05455363669589852</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.09999999999999964</v>
-      </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.96249698464912</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.08811366790778852</v>
+          <t>0.09863145686649402</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>basal_contable</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>93</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3.088333333333333</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3573999999999842</v>
-      </c>
-      <c r="G6" t="n">
-        <v>198.5215367647142</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1800308449272036</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.069663898562371</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.01866943477096195</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.05333333333333323</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.01229913786857884</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.05333333333333323</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.110471781496774</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.04080788293440341</v>
+          <t>False</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>basal_resumen</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>118</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.928333333333334</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.2666000000000395</v>
-      </c>
-      <c r="G7" t="n">
-        <v>198.5397815339569</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1342803935514768</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.868096613855232</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.06023671947810216</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.100000000000001</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.009637073452864353</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.06499999999999995</v>
-      </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.94568006554849</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.07758345169325809</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>129</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.298333333333334</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.2990999999999531</v>
-      </c>
-      <c r="G8" t="n">
-        <v>198.5402841585345</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.1506495275090478</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.263179562520406</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.03515377081292748</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.06166666666666654</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0142805200528846</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.06166666666666654</v>
-      </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4.337642886942003</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.07446332442159687</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>330</v>
-      </c>
-      <c r="E9" t="n">
-        <v>10.98833333333333</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.2684000000000424</v>
-      </c>
-      <c r="G9" t="n">
-        <v>198.4557402139328</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1352442613706767</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10.95795988934993</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.03037344398340203</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.06666666666666998</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.01366737957022401</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.06666666666666998</v>
-      </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>11.01293461655973</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.05497472720980667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1588</v>
-      </c>
-      <c r="E10" t="n">
-        <v>53.88666666666667</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.252399999999966</v>
-      </c>
-      <c r="G10" t="n">
-        <v>198.3541037561349</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.1272471782637164</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>53.83846395901939</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.04820270764727752</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.1049999999999969</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.03770589763574606</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.06666666666666998</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>53.96783602150538</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.1293720624859915</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1595</v>
-      </c>
-      <c r="E11" t="n">
-        <v>54.12333333333333</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.2673000000000343</v>
-      </c>
-      <c r="G11" t="n">
-        <v>198.3520775970489</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.134760373190067</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>54.06799621465152</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.05533711868180546</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.09833333333334338</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.04425000000001234</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.09666666666666401</v>
-      </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>54.18129102564103</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.1132948109895082</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1910</v>
-      </c>
-      <c r="E12" t="n">
-        <v>64.88666666666667</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.3209999999999695</v>
-      </c>
-      <c r="G12" t="n">
-        <v>198.398962020948</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.1617952013106181</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>64.849145785877</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.0375208807896712</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1033333333333246</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.0247268907562983</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.07333333333332348</v>
-      </c>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>64.92800020374898</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.07885441787198033</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1936</v>
-      </c>
-      <c r="E13" t="n">
-        <v>65.75333333333334</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.3229000000000042</v>
-      </c>
-      <c r="G13" t="n">
-        <v>198.4054445865139</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.1627475499338955</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>65.67503623188401</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.07829710144933699</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.03166666666666629</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1316666666666748</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.009304402950661483</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.06666666666667709</v>
-      </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>65.77008125864455</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.09504502676054472</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1942</v>
-      </c>
-      <c r="E14" t="n">
-        <v>65.95333333333333</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2766999999999484</v>
-      </c>
-      <c r="G14" t="n">
-        <v>198.3984303688183</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1394668291909211</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>65.92354505582138</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.02978827751195467</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.06333333333333258</v>
-      </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.03390562952580467</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.09666666666667822</v>
-      </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>66.01309273534223</v>
-      </c>
-      <c r="V14" t="n">
-        <v>3</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.08954767952084808</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1951</v>
-      </c>
-      <c r="E15" t="n">
-        <v>66.25500000000001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.4117999999999711</v>
-      </c>
-      <c r="G15" t="n">
-        <v>198.3514719979033</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.2076112649188326</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>66.17355973025049</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.08144026974952112</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.03333333333333144</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.13333333333334</v>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.01450215005931454</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.06666666666667709</v>
-      </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>66.28110387010678</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.1075441398562873</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1955</v>
-      </c>
-      <c r="E16" t="n">
-        <v>66.38666666666667</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.2730999999999995</v>
-      </c>
-      <c r="G16" t="n">
-        <v>198.3713288408475</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.137671104789093</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="n">
-        <v>66.36151933701657</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.02514732965009614</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.008149806028058038</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="T16" t="b">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>66.40133631751716</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.03981698050058924</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1988</v>
-      </c>
-      <c r="E17" t="n">
-        <v>67.48666666666666</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.3883999999999901</v>
-      </c>
-      <c r="G17" t="n">
-        <v>198.3318002854925</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.1958334464976874</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>67.45808682855041</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.02857983811625786</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.08333333333334281</v>
-      </c>
-      <c r="O17" t="b">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.01768026219956198</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.08333333333334281</v>
-      </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>67.51849113862589</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.06040431007548364</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1991</v>
-      </c>
-      <c r="E18" t="n">
-        <v>67.58833333333334</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5412999999999784</v>
-      </c>
-      <c r="G18" t="n">
-        <v>198.3318002854925</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.2729264793748626</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>67.5436508091246</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.04468252420873853</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.0833333333333286</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.01097666922814255</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>67.60809133794399</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.06444052881938944</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E19" t="n">
-        <v>68.55333333333334</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.314899999999966</v>
-      </c>
-      <c r="G19" t="n">
-        <v>198.3435038480781</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1587649677910121</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>68.53651284126471</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.01682049206863212</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="O19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.0520995956399446</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.08499999999999375</v>
-      </c>
-      <c r="T19" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>68.61761260548523</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.08109976422052512</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2068</v>
-      </c>
-      <c r="E20" t="n">
-        <v>70.155</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.4390999999999963</v>
-      </c>
-      <c r="G20" t="n">
-        <v>198.3756939591885</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.2213476818840173</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>70.05868511685118</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.0963148831488212</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.03333333333333144</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1349999999999909</v>
-      </c>
-      <c r="O20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.01734202211690672</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.06833333333332803</v>
-      </c>
-      <c r="T20" t="b">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>70.18621563981043</v>
-      </c>
-      <c r="V20" t="n">
-        <v>4</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1275305229592476</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2075</v>
-      </c>
-      <c r="E21" t="n">
-        <v>70.38500000000001</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.8859999999999673</v>
-      </c>
-      <c r="G21" t="n">
-        <v>198.3831499079263</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4466105112310083</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>70.35108214849922</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.03391785150078874</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="O21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.01144364897778871</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="T21" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>70.40559856816002</v>
-      </c>
-      <c r="V21" t="n">
-        <v>3</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.0545164196607999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2081</v>
-      </c>
-      <c r="E22" t="n">
-        <v>70.59166666666667</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1.044100000000014</v>
-      </c>
-      <c r="G22" t="n">
-        <v>198.3831499079263</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5263047796572454</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>70.55716666666667</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.0344999999999942</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.06666666666666288</v>
-      </c>
-      <c r="O22" t="b">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.03027929017947883</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.09999999999999432</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>70.63878967533778</v>
-      </c>
-      <c r="V22" t="n">
-        <v>3</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.08162300867110162</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2088</v>
-      </c>
-      <c r="E23" t="n">
-        <v>70.82000000000002</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5156999999999812</v>
-      </c>
-      <c r="G23" t="n">
-        <v>198.3740520613614</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.2599634350567502</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>70.78578041828833</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.03421958171169592</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.1016666666666595</v>
-      </c>
-      <c r="O23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.0188637270550629</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.06999999999999318</v>
-      </c>
-      <c r="T23" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>70.85395470869912</v>
-      </c>
-      <c r="V23" t="n">
-        <v>3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.06817429041079492</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2115</v>
-      </c>
-      <c r="E24" t="n">
-        <v>71.72</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.3376999999999839</v>
-      </c>
-      <c r="G24" t="n">
-        <v>198.3268287958707</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1702744918830745</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>71.7060837912088</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.01391620879120126</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.06666666666667709</v>
-      </c>
-      <c r="O24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.03635092299087717</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.1000000000000085</v>
-      </c>
-      <c r="T24" t="b">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>71.76474672136243</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.05866293015363055</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>espontaneos</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2119</v>
-      </c>
-      <c r="E25" t="n">
-        <v>71.85333333333334</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.36099999999999</v>
-      </c>
-      <c r="G25" t="n">
-        <v>198.3050778989556</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1820427413280531</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>71.83790598290599</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.01542735042734478</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.06666666666664867</v>
-      </c>
-      <c r="O25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.01489273927393242</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.06666666666664867</v>
-      </c>
-      <c r="T25" t="b">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>71.88014026402641</v>
-      </c>
-      <c r="V25" t="n">
-        <v>2</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.04223428112041461</v>
+          <t>no contable (conteo NO reportable); actividad basal 0.10 % del grosor</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4408,262 +3150,2107 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cinetica_min_frames</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>n_eventos_cinetica</t>
+          <t>tren</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_iqr_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ttp_n_eventos</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ttp_n_medibles</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ttp_frames_mediana</t>
+          <t>meseta_pico_frames</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ttp_reportable</t>
+          <t>frame_llega_max</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>tiempo_llega_max_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pico_dudoso_por_ruido</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_iqr_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_cota_inf_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_cota_sup_s</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_n_eventos</t>
-        </is>
-      </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>rt50_n_medibles</t>
+          <t>ttp_min_s</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>rt50_frames_mediana</t>
+          <t>ttp_max_s</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>rt50_reportable</t>
+          <t>ttp_medible</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>rt50_iqr_s</t>
-        </is>
-      </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>rt50_cota_inf_s</t>
+          <t>rt50_min_s</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>rt50_cota_sup_s</t>
+          <t>rt50_max_s</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>cinetica_motivo</t>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>todos</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3866666666666668</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2597000000000094</v>
+      </c>
+      <c r="G2" t="n">
+        <v>198.4641410543336</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1308548731374658</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.3866666666666668</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3309397408858161</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05572692578085076</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.04061667954993881</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.09833333333333344</v>
+      </c>
+      <c r="W2" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4451275444473077</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1141878035614916</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.386666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3187999999999533</v>
+      </c>
+      <c r="G3" t="n">
+        <v>198.5183571723238</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1605896827582646</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.386666666666667</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.357911405091201</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02875526157546604</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07833333333333403</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01224688407034202</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.07833333333333403</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.408711057993282</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.05079965290208155</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>62</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.053333333333334</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2863000000000397</v>
+      </c>
+      <c r="G4" t="n">
+        <v>198.5208372907626</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.144216599077059</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>62</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.053333333333334</v>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.02053837342497</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0327949599083639</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.06666666666666687</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.02055866724112887</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.06666666666666687</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.127349999999997</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.106811626575027</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>87</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.886666666666667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2531000000000176</v>
+      </c>
+      <c r="G5" t="n">
+        <v>198.5215471224989</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1274924579566372</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>87</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.886666666666667</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.874383316741331</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01228334992533586</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.06166666666666698</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.05455363669589852</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.09999999999999964</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.96249698464912</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.08811366790778852</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.088333333333333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3573999999999842</v>
+      </c>
+      <c r="G6" t="n">
+        <v>198.5215367647142</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1800308449272036</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>93</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.088333333333333</v>
+      </c>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.069663898562371</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01866943477096195</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.05333333333333323</v>
+      </c>
+      <c r="R6" t="b">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.01229913786857884</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05333333333333323</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.110471781496774</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.04080788293440341</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>118</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.928333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2666000000000395</v>
+      </c>
+      <c r="G7" t="n">
+        <v>198.5397815339569</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1342803935514768</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>118</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.928333333333334</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.868096613855232</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06023671947810216</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.100000000000001</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.009637073452864353</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.06499999999999995</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.94568006554849</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.07758345169325809</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>129</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.298333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2990999999999531</v>
+      </c>
+      <c r="G8" t="n">
+        <v>198.5402841585345</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1506495275090478</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>129</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.298333333333334</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.263179562520406</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03515377081292748</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.06166666666666654</v>
+      </c>
+      <c r="R8" t="b">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0142805200528846</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.06166666666666654</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.337642886942003</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.07446332442159687</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>330</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.98833333333333</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2684000000000424</v>
+      </c>
+      <c r="G9" t="n">
+        <v>198.4557402139328</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1352442613706767</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>330</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.98833333333333</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10.95795988934993</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03037344398340203</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.06666666666666998</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.01366737957022401</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.06666666666666998</v>
+      </c>
+      <c r="W9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11.01293461655973</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.05497472720980667</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1588</v>
+      </c>
+      <c r="E10" t="n">
+        <v>53.88666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.252399999999966</v>
+      </c>
+      <c r="G10" t="n">
+        <v>198.3541037561349</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1272471782637164</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1588</v>
+      </c>
+      <c r="K10" t="n">
+        <v>53.88666666666667</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>53.83846395901939</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04820270764727752</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1049999999999969</v>
+      </c>
+      <c r="R10" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.03770589763574606</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06666666666666998</v>
+      </c>
+      <c r="W10" t="b">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>53.96783602150538</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1293720624859915</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E11" t="n">
+        <v>54.12333333333333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2673000000000343</v>
+      </c>
+      <c r="G11" t="n">
+        <v>198.3520775970489</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.134760373190067</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1595</v>
+      </c>
+      <c r="K11" t="n">
+        <v>54.12333333333333</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54.06799621465152</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05533711868180546</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.09833333333334338</v>
+      </c>
+      <c r="R11" t="b">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.04425000000001234</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.09666666666666401</v>
+      </c>
+      <c r="W11" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>54.18129102564103</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1132948109895082</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="E12" t="n">
+        <v>64.88666666666667</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3209999999999695</v>
+      </c>
+      <c r="G12" t="n">
+        <v>198.398962020948</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1617952013106181</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="K12" t="n">
+        <v>64.88666666666667</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>64.849145785877</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0375208807896712</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1033333333333246</v>
+      </c>
+      <c r="R12" t="b">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.0247268907562983</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.07333333333332348</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>64.92800020374898</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.07885441787198033</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1936</v>
+      </c>
+      <c r="E13" t="n">
+        <v>65.75333333333334</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3229000000000042</v>
+      </c>
+      <c r="G13" t="n">
+        <v>198.4054445865139</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1627475499338955</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1936</v>
+      </c>
+      <c r="K13" t="n">
+        <v>65.75333333333334</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>65.67503623188401</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07829710144933699</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.03166666666666629</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1316666666666748</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.009304402950661483</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.06666666666667709</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>65.77008125864455</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.09504502676054472</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1942</v>
+      </c>
+      <c r="E14" t="n">
+        <v>65.95333333333333</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2766999999999484</v>
+      </c>
+      <c r="G14" t="n">
+        <v>198.3984303688183</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1394668291909211</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1942</v>
+      </c>
+      <c r="K14" t="n">
+        <v>65.95333333333333</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>65.92354505582138</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.02978827751195467</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.06333333333333258</v>
+      </c>
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.03390562952580467</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.09666666666667822</v>
+      </c>
+      <c r="W14" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>66.01309273534223</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.08954767952084808</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E15" t="n">
+        <v>66.25500000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4117999999999711</v>
+      </c>
+      <c r="G15" t="n">
+        <v>198.3514719979033</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2076112649188326</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1951</v>
+      </c>
+      <c r="K15" t="n">
+        <v>66.25500000000001</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>66.17355973025049</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.08144026974952112</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.03333333333333144</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.13333333333334</v>
+      </c>
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01450215005931454</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.06666666666667709</v>
+      </c>
+      <c r="W15" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>66.28110387010678</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.1075441398562873</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E16" t="n">
+        <v>66.38666666666667</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2730999999999995</v>
+      </c>
+      <c r="G16" t="n">
+        <v>198.3713288408475</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.137671104789093</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K16" t="n">
+        <v>66.38666666666667</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>66.36151933701657</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.02514732965009614</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="R16" t="b">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.008149806028058038</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="W16" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>66.40133631751716</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.03981698050058924</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1988</v>
+      </c>
+      <c r="E17" t="n">
+        <v>67.48666666666666</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3883999999999901</v>
+      </c>
+      <c r="G17" t="n">
+        <v>198.3318002854925</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1958334464976874</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1988</v>
+      </c>
+      <c r="K17" t="n">
+        <v>67.48666666666666</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>67.45808682855041</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.02857983811625786</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.08333333333334281</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.01768026219956198</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.08333333333334281</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>67.51849113862589</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.06040431007548364</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="E18" t="n">
+        <v>67.58833333333334</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5412999999999784</v>
+      </c>
+      <c r="G18" t="n">
+        <v>198.3318002854925</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2729264793748626</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="K18" t="n">
+        <v>67.58833333333334</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67.5436508091246</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04468252420873853</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.0833333333333286</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.01097666922814255</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>67.60809133794399</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.06444052881938944</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E19" t="n">
+        <v>68.55333333333334</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.314899999999966</v>
+      </c>
+      <c r="G19" t="n">
+        <v>198.3435038480781</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1587649677910121</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K19" t="n">
+        <v>68.55333333333334</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>68.53651284126471</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01682049206863212</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.0520995956399446</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.08499999999999375</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>68.61761260548523</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.08109976422052512</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2068</v>
+      </c>
+      <c r="E20" t="n">
+        <v>70.155</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4390999999999963</v>
+      </c>
+      <c r="G20" t="n">
+        <v>198.3756939591885</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2213476818840173</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2068</v>
+      </c>
+      <c r="K20" t="n">
+        <v>70.155</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>70.05868511685118</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0963148831488212</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.03333333333333144</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1349999999999909</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.01734202211690672</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.06833333333332803</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>70.18621563981043</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.1275305229592476</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2075</v>
+      </c>
+      <c r="E21" t="n">
+        <v>70.38500000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8859999999999673</v>
+      </c>
+      <c r="G21" t="n">
+        <v>198.3831499079263</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4466105112310083</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2075</v>
+      </c>
+      <c r="K21" t="n">
+        <v>70.38500000000001</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>70.35108214849922</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.03391785150078874</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.01144364897778871</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>70.40559856816002</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.0545164196607999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2081</v>
+      </c>
+      <c r="E22" t="n">
+        <v>70.59166666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.044100000000014</v>
+      </c>
+      <c r="G22" t="n">
+        <v>198.3831499079263</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5263047796572454</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2081</v>
+      </c>
+      <c r="K22" t="n">
+        <v>70.59166666666667</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>70.55716666666667</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0344999999999942</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.06666666666666288</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.03027929017947883</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>70.63878967533778</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.08162300867110162</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2088</v>
+      </c>
+      <c r="E23" t="n">
+        <v>70.82000000000002</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5156999999999812</v>
+      </c>
+      <c r="G23" t="n">
+        <v>198.3740520613614</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2599634350567502</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2088</v>
+      </c>
+      <c r="K23" t="n">
+        <v>70.82000000000002</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>70.78578041828833</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.03421958171169592</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1016666666666595</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.0188637270550629</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.06999999999999318</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>70.85395470869912</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.06817429041079492</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>espontaneos</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2115</v>
+      </c>
+      <c r="E24" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3376999999999839</v>
+      </c>
+      <c r="G24" t="n">
+        <v>198.3268287958707</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1702744918830745</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2115</v>
+      </c>
+      <c r="K24" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>71.7060837912088</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.01391620879120126</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.06666666666667709</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.03635092299087717</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.1000000000000085</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>71.76474672136243</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.05866293015363055</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.1611924420344413</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.1371-0.1988</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3198999999999614</v>
-      </c>
-      <c r="G2" t="n">
-        <v>24</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.08083333333333131</v>
-      </c>
-      <c r="O2" t="n">
-        <v>24</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.06750000000000256</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>espontaneos</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1611924420344413</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.1371-0.1988</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3198999999999614</v>
-      </c>
-      <c r="G3" t="n">
-        <v>24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.08083333333333131</v>
-      </c>
-      <c r="O3" t="n">
-        <v>24</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="b">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.06750000000000256</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
-        </is>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2119</v>
+      </c>
+      <c r="E25" t="n">
+        <v>71.85333333333334</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.36099999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>198.3050778989556</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1820427413280531</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2119</v>
+      </c>
+      <c r="K25" t="n">
+        <v>71.85333333333334</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>71.83790598290599</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.01542735042734478</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.06666666666664867</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.01489273927393242</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.06666666666664867</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>71.88014026402641</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.04223428112041461</v>
       </c>
     </row>
   </sheetData>
